--- a/prodinfo/mea/sa/output/res20260307.xlsx
+++ b/prodinfo/mea/sa/output/res20260307.xlsx
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-03-07 05:15:11</v>
+        <v>2026-03-07 06:00:31</v>
       </c>
       <c r="B2" t="str">
         <v>沙特</v>
@@ -447,7 +447,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-03-07 05:15:15</v>
+        <v>2026-03-07 06:00:35</v>
       </c>
       <c r="B3" t="str">
         <v>沙特</v>
@@ -470,7 +470,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-03-07 05:15:20</v>
+        <v>2026-03-07 06:00:40</v>
       </c>
       <c r="B4" t="str">
         <v>沙特</v>
@@ -493,7 +493,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-03-07 05:15:23</v>
+        <v>2026-03-07 06:00:44</v>
       </c>
       <c r="B5" t="str">
         <v>沙特</v>
@@ -516,7 +516,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-03-07 05:15:27</v>
+        <v>2026-03-07 06:00:48</v>
       </c>
       <c r="B6" t="str">
         <v>沙特</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-03-07 05:15:31</v>
+        <v>2026-03-07 06:00:52</v>
       </c>
       <c r="B7" t="str">
         <v>沙特</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-03-07 05:15:37</v>
+        <v>2026-03-07 06:00:55</v>
       </c>
       <c r="B8" t="str">
         <v>沙特</v>
@@ -585,7 +585,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-03-07 05:15:39</v>
+        <v>2026-03-07 06:01:00</v>
       </c>
       <c r="B9" t="str">
         <v>沙特</v>
@@ -608,7 +608,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-03-07 05:15:44</v>
+        <v>2026-03-07 06:01:04</v>
       </c>
       <c r="B10" t="str">
         <v>沙特</v>
@@ -631,7 +631,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-03-07 05:15:48</v>
+        <v>2026-03-07 06:01:09</v>
       </c>
       <c r="B11" t="str">
         <v>沙特</v>
@@ -654,7 +654,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-03-07 05:15:54</v>
+        <v>2026-03-07 06:01:12</v>
       </c>
       <c r="B12" t="str">
         <v>沙特</v>
@@ -677,7 +677,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-03-07 05:16:00</v>
+        <v>2026-03-07 06:01:18</v>
       </c>
       <c r="B13" t="str">
         <v>沙特</v>
@@ -700,7 +700,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-03-07 05:16:04</v>
+        <v>2026-03-07 06:01:24</v>
       </c>
       <c r="B14" t="str">
         <v>沙特</v>
@@ -723,7 +723,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-03-07 05:16:08</v>
+        <v>2026-03-07 06:01:28</v>
       </c>
       <c r="B15" t="str">
         <v>沙特</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-03-07 05:16:11</v>
+        <v>2026-03-07 06:01:34</v>
       </c>
       <c r="B16" t="str">
         <v>沙特</v>
@@ -769,7 +769,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-03-07 05:16:14</v>
+        <v>2026-03-07 06:01:37</v>
       </c>
       <c r="B17" t="str">
         <v>沙特</v>
@@ -792,7 +792,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-03-07 05:16:20</v>
+        <v>2026-03-07 06:01:41</v>
       </c>
       <c r="B18" t="str">
         <v>沙特</v>
@@ -815,7 +815,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-03-07 05:16:24</v>
+        <v>2026-03-07 06:01:45</v>
       </c>
       <c r="B19" t="str">
         <v>沙特</v>
@@ -838,7 +838,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-03-07 05:16:28</v>
+        <v>2026-03-07 06:01:49</v>
       </c>
       <c r="B20" t="str">
         <v>沙特</v>
@@ -861,7 +861,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-03-07 05:16:34</v>
+        <v>2026-03-07 06:01:52</v>
       </c>
       <c r="B21" t="str">
         <v>沙特</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-03-07 05:16:39</v>
+        <v>2026-03-07 06:01:56</v>
       </c>
       <c r="B22" t="str">
         <v>沙特</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-03-07 05:16:43</v>
+        <v>2026-03-07 06:02:02</v>
       </c>
       <c r="B23" t="str">
         <v>沙特</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-03-07 05:16:47</v>
+        <v>2026-03-07 06:02:08</v>
       </c>
       <c r="B24" t="str">
         <v>沙特</v>
@@ -953,7 +953,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-03-07 05:16:52</v>
+        <v>2026-03-07 06:02:12</v>
       </c>
       <c r="B25" t="str">
         <v>沙特</v>
@@ -976,7 +976,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-03-07 05:16:57</v>
+        <v>2026-03-07 06:02:18</v>
       </c>
       <c r="B26" t="str">
         <v>沙特</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-03-07 05:17:04</v>
+        <v>2026-03-07 06:02:21</v>
       </c>
       <c r="B27" t="str">
         <v>沙特</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-03-07 05:17:07</v>
+        <v>2026-03-07 06:02:24</v>
       </c>
       <c r="B28" t="str">
         <v>沙特</v>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-03-07 05:17:12</v>
+        <v>2026-03-07 06:02:28</v>
       </c>
       <c r="B29" t="str">
         <v>沙特</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-03-07 05:17:15</v>
+        <v>2026-03-07 06:02:32</v>
       </c>
       <c r="B30" t="str">
         <v>沙特</v>
@@ -1091,7 +1091,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-03-07 05:17:20</v>
+        <v>2026-03-07 06:02:35</v>
       </c>
       <c r="B31" t="str">
         <v>沙特</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-03-07 05:17:24</v>
+        <v>2026-03-07 06:02:40</v>
       </c>
       <c r="B32" t="str">
         <v>沙特</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-03-07 05:17:27</v>
+        <v>2026-03-07 06:02:45</v>
       </c>
       <c r="B33" t="str">
         <v>沙特</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-03-07 05:17:32</v>
+        <v>2026-03-07 06:02:50</v>
       </c>
       <c r="B34" t="str">
         <v>沙特</v>
@@ -1183,7 +1183,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-03-07 05:17:34</v>
+        <v>2026-03-07 06:02:56</v>
       </c>
       <c r="B35" t="str">
         <v>沙特</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-03-07 05:17:39</v>
+        <v>2026-03-07 06:02:59</v>
       </c>
       <c r="B36" t="str">
         <v>沙特</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-03-07 05:17:44</v>
+        <v>2026-03-07 06:03:03</v>
       </c>
       <c r="B37" t="str">
         <v>沙特</v>
@@ -1252,7 +1252,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-03-07 05:17:48</v>
+        <v>2026-03-07 06:03:06</v>
       </c>
       <c r="B38" t="str">
         <v>沙特</v>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-03-07 05:17:54</v>
+        <v>2026-03-07 06:03:12</v>
       </c>
       <c r="B39" t="str">
         <v>沙特</v>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-03-07 05:17:58</v>
+        <v>2026-03-07 06:03:18</v>
       </c>
       <c r="B40" t="str">
         <v>沙特</v>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-03-07 05:18:04</v>
+        <v>2026-03-07 06:03:24</v>
       </c>
       <c r="B41" t="str">
         <v>沙特</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-03-07 05:18:10</v>
+        <v>2026-03-07 06:03:30</v>
       </c>
       <c r="B42" t="str">
         <v>沙特</v>
@@ -1367,7 +1367,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-03-07 05:18:15</v>
+        <v>2026-03-07 06:03:33</v>
       </c>
       <c r="B43" t="str">
         <v>沙特</v>
@@ -1390,7 +1390,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-03-07 05:18:20</v>
+        <v>2026-03-07 06:03:39</v>
       </c>
       <c r="B44" t="str">
         <v>沙特</v>
@@ -1413,7 +1413,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-03-07 05:18:24</v>
+        <v>2026-03-07 06:03:42</v>
       </c>
       <c r="B45" t="str">
         <v>沙特</v>
@@ -1436,7 +1436,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-03-07 05:18:27</v>
+        <v>2026-03-07 06:03:46</v>
       </c>
       <c r="B46" t="str">
         <v>沙特</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-03-07 05:18:33</v>
+        <v>2026-03-07 06:03:51</v>
       </c>
       <c r="B47" t="str">
         <v>沙特</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-03-07 05:18:37</v>
+        <v>2026-03-07 06:03:54</v>
       </c>
       <c r="B48" t="str">
         <v>沙特</v>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-03-07 05:18:44</v>
+        <v>2026-03-07 06:03:59</v>
       </c>
       <c r="B49" t="str">
         <v>沙特</v>
@@ -1528,7 +1528,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-03-07 05:18:49</v>
+        <v>2026-03-07 06:04:03</v>
       </c>
       <c r="B50" t="str">
         <v>沙特</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-03-07 05:18:55</v>
+        <v>2026-03-07 06:04:06</v>
       </c>
       <c r="B51" t="str">
         <v>沙特</v>
@@ -1574,7 +1574,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026-03-07 05:18:58</v>
+        <v>2026-03-07 06:04:09</v>
       </c>
       <c r="B52" t="str">
         <v>沙特</v>
@@ -1597,7 +1597,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026-03-07 05:19:01</v>
+        <v>2026-03-07 06:04:14</v>
       </c>
       <c r="B53" t="str">
         <v>沙特</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026-03-07 05:19:05</v>
+        <v>2026-03-07 06:04:19</v>
       </c>
       <c r="B54" t="str">
         <v>沙特</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-03-07 05:19:08</v>
+        <v>2026-03-07 06:04:22</v>
       </c>
       <c r="B55" t="str">
         <v>沙特</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-03-07 05:19:13</v>
+        <v>2026-03-07 06:04:24</v>
       </c>
       <c r="B56" t="str">
         <v>沙特</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-03-07 05:19:17</v>
+        <v>2026-03-07 06:04:27</v>
       </c>
       <c r="B57" t="str">
         <v>沙特</v>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-03-07 05:19:19</v>
+        <v>2026-03-07 06:04:32</v>
       </c>
       <c r="B58" t="str">
         <v>沙特</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-03-07 05:19:21</v>
+        <v>2026-03-07 06:04:38</v>
       </c>
       <c r="B59" t="str">
         <v>沙特</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-03-07 05:19:24</v>
+        <v>2026-03-07 06:04:41</v>
       </c>
       <c r="B60" t="str">
         <v>沙特</v>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-03-07 05:19:29</v>
+        <v>2026-03-07 06:04:44</v>
       </c>
       <c r="B61" t="str">
         <v>沙特</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-03-07 05:19:33</v>
+        <v>2026-03-07 06:04:49</v>
       </c>
       <c r="B62" t="str">
         <v>沙特</v>
@@ -1827,7 +1827,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-03-07 05:19:37</v>
+        <v>2026-03-07 06:04:51</v>
       </c>
       <c r="B63" t="str">
         <v>沙特</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-03-07 05:19:42</v>
+        <v>2026-03-07 06:04:56</v>
       </c>
       <c r="B64" t="str">
         <v>沙特</v>
@@ -1873,7 +1873,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026-03-07 05:19:46</v>
+        <v>2026-03-07 06:05:00</v>
       </c>
       <c r="B65" t="str">
         <v>沙特</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-03-07 05:19:48</v>
+        <v>2026-03-07 06:05:05</v>
       </c>
       <c r="B66" t="str">
         <v>沙特</v>
@@ -1919,7 +1919,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026-03-07 05:19:54</v>
+        <v>2026-03-07 06:05:10</v>
       </c>
       <c r="B67" t="str">
         <v>沙特</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026-03-07 05:19:58</v>
+        <v>2026-03-07 06:05:13</v>
       </c>
       <c r="B68" t="str">
         <v>沙特</v>
@@ -1965,7 +1965,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-03-07 05:20:02</v>
+        <v>2026-03-07 06:05:16</v>
       </c>
       <c r="B69" t="str">
         <v>沙特</v>
@@ -1988,7 +1988,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026-03-07 05:20:08</v>
+        <v>2026-03-07 06:05:21</v>
       </c>
       <c r="B70" t="str">
         <v>沙特</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026-03-07 05:20:13</v>
+        <v>2026-03-07 06:05:24</v>
       </c>
       <c r="B71" t="str">
         <v>沙特</v>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026-03-07 05:20:18</v>
+        <v>2026-03-07 06:05:28</v>
       </c>
       <c r="B72" t="str">
         <v>沙特</v>
@@ -2057,7 +2057,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026-03-07 05:20:21</v>
+        <v>2026-03-07 06:05:30</v>
       </c>
       <c r="B73" t="str">
         <v>沙特</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2026-03-07 05:20:25</v>
+        <v>2026-03-07 06:05:35</v>
       </c>
       <c r="B74" t="str">
         <v>沙特</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2026-03-07 05:20:30</v>
+        <v>2026-03-07 06:05:38</v>
       </c>
       <c r="B75" t="str">
         <v>沙特</v>
@@ -2126,7 +2126,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2026-03-07 05:20:32</v>
+        <v>2026-03-07 06:05:40</v>
       </c>
       <c r="B76" t="str">
         <v>沙特</v>
@@ -2149,7 +2149,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2026-03-07 05:20:36</v>
+        <v>2026-03-07 06:05:43</v>
       </c>
       <c r="B77" t="str">
         <v>沙特</v>
